--- a/extenbooks/S707_extenbook.xlsx
+++ b/extenbooks/S707_extenbook.xlsx
@@ -17133,7 +17133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A158"/>
+  <dimension ref="A1:A206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17413,194 +17413,202 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>**S707** is the time-series exhibit Shaikh displays in Fig7.19. Period: 1962–1991.</t>
+          <t>**S707** is the exhibit Shaikh displays in Fig7.19 — the deviations of twenty Greek manufacturing</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>industries' average rates of profit (ROP) from the overall average rate, 1962–1991.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Per the playbook recipe for `content_type = data_unavailable`:</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Following the 2026-05-26 recovery (§0), this is a **digitized book-period series**, not a</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>&gt; "DPR + EPR documenting the chart-only source and why no underlying data exists ... L01 returns SKIPPED ... V03 returns PASS_DATA_UNAVAILABLE ... No chopped CSV."</t>
+          <t>`data_unavailable` one: the loader (`L01_S707`) reads the digitized panel workbook and emits the</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>series, the validator (`V03_S707`) round-trips against it, and a chopped CSV is produced. (The</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>earlier `data_unavailable` handling — loader SKIPPED, validator `PASS_DATA_UNAVAILABLE`, no CSV — no</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>longer applies; it is retained below only as historical context.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>## 2. Why it matters in Chapter 7</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Ch7's empirical case for turbulent profit-rate equalization layers several exhibits: US BEA (S705–S710), the **Greek manufacturing pair (S707/S708)**, OECD STAN (S711), and the Christodoulopoulos (1995) world/US ISDB reconstruction (S703/S704). **S707 is the Greek manufacturing exhibit, not the Christodoulopoulos one** — it is Shaikh's Fig 7.19, *"Deviations of Greek Manufacturing Profit Rates from Average Profit Rate, 1962–1991"*, reproduced from Tsoulfidis &amp; Tsaliki (2011, p.19, fig. 4) (book ref. confirmed). S708 is its incremental-rate companion (Fig 7.20 = Tsoulfidis &amp; Tsaliki 2011 fig. 5). Tsoulfidis &amp; Tsaliki publish these as charts only; the raw 1962–1991 data is no longer recoverable from the workspace but the published figures remain as historical attestation. *(Christodoulopoulos belongs to S703/S704 — a separate exhibit; an earlier draft of this paragraph conflated the two.)*</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>## 3. Sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-    </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>| Subseries | Coverage | Publisher | Status |</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>| S707-A (20 industries, digitized) | 1962–1991 | TSOULFIDIS_TSALIKI_2011_FIG4 | **book_period_validated** (provenance: digitized) |</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>| Subseries | Coverage | Publisher | Status |</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tsoulfidis &amp; Tsaliki (2011) publish fig. 4 as a chart only — no underlying table — and the year-by-year 1962–1991 data exists only with the authors. The UoM Discussion Paper 2011_02 hosted PDF is dead (HTTP 500, confirmed via RePEc/EconPapers). No salvaged copy is in `SalvagedInputs`; the Phase 4 B5 search documented this explicitly at `SalvagedInputs/book_data/Reconstructed/Tsoulfidis_Tsaliki_2011_data_unavailable.md` (for S707/S708). *(The companion note `Christodoulopoulos_1995_data_unavailable.md` covers the separate S703/S704 exhibit.)*</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>| S707-A (20 industries, digitized) | 1962–1991 | TSOULFIDIS_TSALIKI_2011_FIG4 | **book_period_validated** (provenance: digitized) |</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>## 4. Construction</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Tsoulfidis &amp; Tsaliki (2011) publish fig. 4 as a chart only — no underlying table — so the authors' exact year-by-year 1962–1991 table is not redistributed. The original University of Macedonia (UoM) Discussion Paper 2011_02 PDF is dead (HTTP 500, confirmed via RePEc/EconPapers), but a live full-text copy survives on MPRA (working paper 51334), and the plotted panel was recovered from it by offline vector digitization (§0). The earlier readiness-review (Phase 4) search — which predates that recovery — recorded the dead-source finding at `SalvagedInputs/book_data/Reconstructed/Tsoulfidis_Tsaliki_2011_data_unavailable.md`; that note is retained as history and is superseded by the 2026-05-26 recovery. *(The companion note `Christodoulopoulos_1995_data_unavailable.md` covers the separate S703/S704 exhibit, which remains genuinely data_unavailable.)*</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Digitized industry panel (1962–1991, 20 two-digit Greek manufacturing industries):</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>- `L01_S707` reads the digitized panel xlsx and emits long-form deviations via the shared</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  `_ch7_xlsx_panels.deviations_long` (subseries `S707-A-&lt;industry&gt;`).</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>- `P02_S707` canonicalises the schema via the shared `_ch7_industry_panel_processor`</t>
+          <t>Digitized industry panel (1962–1991, 20 two-digit Greek manufacturing industries):</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (preserves the `industry` column) → `data/processed/S707.parquet`.</t>
+          <t>- `L01_S707` reads the digitized panel xlsx and emits long-form deviations via the shared</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>- `V03_S707` round-trips against the panel's `*_Deviation` columns (`is_deviation=True`):</t>
+          <t xml:space="preserve">  `_ch7_xlsx_panels.deviations_long` (subseries `S707-A-&lt;industry&gt;`).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PASS, n=600, MAE 0.0 (certifies loader/processor fidelity over the digitized source).</t>
+          <t>- `P02_S707` canonicalises the schema via the shared `_ch7_industry_panel_processor`</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>- Chopped: `chopped/S707.csv` (long: year, value, subseries_id, source_id, units, industry).</t>
+          <t xml:space="preserve">  (preserves the `industry` column) → `data/processed/S707.parquet`.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>- Extenbook: `extenbooks/S707_extenbook.xlsx`.</t>
+          <t>- `V03_S707` round-trips against the panel's `*_Deviation` columns (`is_deviation=True`):</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PASS, n=600, MAE 0.0 (certifies loader/processor fidelity over the digitized source).</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>- Chopped: `chopped/S707.csv` (long: year, value, subseries_id, source_id, units, industry).</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>- Extenbook: `extenbooks/S707_extenbook.xlsx`.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>- **Book period**: 1962–1991</t>
-        </is>
-      </c>
+      <c r="A78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>- **Extension period**: not applicable (data_unavailable)</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
@@ -17610,252 +17618,260 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>- **Book period**: 1962–1991</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>- **Extension period**: not applicable (no faithful time-extension of the Greek panel; see `S707_EPR.md` §2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>## 6. Units</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>rate deviation (decimal).</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr"/>
-    </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>1. **No byte-exact reproduction possible** from local materials. The published figure stands as the authoritative record.</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2. **PDF digitization** (WebPlotDigitizer) is technically possible but is a Phase 9 visualization task, not a Phase 5 data-ingestion task — and would introduce digitization noise that the No-Synthetic rule discourages for primary data.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>3. **No modern substitute** can splice onto the discontinued ISDB / unredistributed T&amp;T panel without violating the Anti-Degradation rule (industry-mapping drift, country-coverage drift, ESYE→ELSTAT methodology break). Any modern continuation is methodologically separate, not an extension.</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1. **Digitization-grade, not table-exact.** The series was recovered by offline vector digitization of the source figure (§0), so it is faithful to the published chart rather than to the authors' exact underlying table (obtainable only by author request). The published figure remains the authoritative record.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>2. **Digitization was performed as the book-period recovery**, using offline PDF vector extraction (no API calls), per-panel y-axis calibration, and clipping to 1962–1991. It is disclosed as `provenance: digitized` and validated against the paper's own aggregate moments (§0); it is a documented recovery of the authors' plotted points, not synthetic infill.</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>3. **No modern substitute** can splice onto the unredistributed Tsoulfidis &amp; Tsaliki Greek panel without violating the Anti-Degradation rule (industry-mapping drift and the 2010 ESYE→ELSTAT methodology break). Any modern continuation is methodologically separate, not an extension. *(The discontinued OECD-ISDB world/US splice concern belongs to the separate S703/S704 exhibit, not this Greek panel.)*</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>- **CD legacy ID**: `S038`</t>
-        </is>
-      </c>
+      <c r="A93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 7 (Fig7.19); Appendix 7.1 II / IV (book pp. 856, 859).</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>- **B5 provenance document**: see SalvagedInputs/book_data/Reconstructed/ for the relevant `*_data_unavailable.md`.</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>- **CD legacy ID**: `S038`</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>## 9. Validation</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 7 (Fig7.19); Appendix 7.1, sub-sections II / IV (book pp. 856, 859).</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>- **Recovery documentation**: `Technical/WL1_Tsoulfidis_Tsaliki/EXTRACTION_REPORT.md` and the digitized workbook `SalvagedInputs/book_data/Reconstructed/Tsoulfidis_Tsaliki_2011_Fig4_S707.xlsx` (supersedes the earlier `*_data_unavailable.md` marker note, which predates the 2026-05-26 recovery).</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>- **V03 status**: `PASS` (is_deviation_panel; n_compared=600; MAE 0.0; max_pct_err 0.0) — round-trip</t>
-        </is>
-      </c>
+      <c r="A99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">  against the digitized panel's `*_Deviation` columns.</t>
+          <t>## 9. Validation</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>- **Registry reference_values** (Decision 0002): subseries `S707-A-20-Food` at 1965/1975/1985 =</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0153 / 0.0142 / 0.1106 (tolerance 0.02). Spot anchors read from the digitized figure —</t>
+          <t>- **V03 status**: `PASS` (is_deviation_panel; n_compared=600; MAE 0.0; max_pct_err 0.0) — round-trip</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">  provenance: digitized, not an independent published table.</t>
+          <t xml:space="preserve">  against the digitized panel's `*_Deviation` columns.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>- **Fidelity note**: values are digitization-grade. The Fig-5 aggregate validation (§0) is the</t>
+          <t>- **Registry reference_values** (Decision 0002): subseries `S707-A-20-Food` at 1965/1975/1985 =</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t xml:space="preserve">  0.0153 / 0.0142 / 0.1106 (tolerance 0.02). Spot anchors read from the digitized figure —</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  provenance: digitized, not an independent published table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>- **Fidelity note**: values are digitization-grade. The Fig-5 aggregate validation (§0) is the</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t xml:space="preserve">  external confidence anchor; the authors' exact panel remains obtainable only by request.</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="4">
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>- **ROP** — (average) rate of profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>- **IROP** — incremental rate of profit: the return on newly added capital (year-to-year change in profit over new investment); the subject of the companion series S708.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>- **Deviation** — an industry's rate minus the overall average rate that year; equalisation shows up as deviations crossing zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>- **Subseries (S707-A)** — a data line within series S707; here S707-A holds the 20-industry digitized panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>- **ESYE / ELSTAT** — the Greek national statistical service and its post-2010 successor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>- **ISDB** — OECD International Sectoral Database (relevant to the separate S703/S704 exhibit, not this Greek panel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>- **MPRA** — the Munich Personal RePEc Archive, which hosts the full-text source paper (working paper 51334).</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>- **L01 / V03** — the load and validate scripts that build and check the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset (legacy ID S038).</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>- **Phase 5 / Phase 6** — Anu pipeline stages: ingestion / extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4">
         <f>== EPR: S707_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t># S707 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>**Series**: S707 — Figure 7.19 — Greek Manufacturing ROP Deviations, 1962–1991 (Tsoulfidis &amp; Tsaliki 2011 Fig 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `data_unavailable`</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>**Extension method**: not applicable — see §1</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>**Author**: opus-subagent-ch7-fanout</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>**Related**: `S707_DPR.md`</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>## 1. Classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>`content_type = data_unavailable`. There is no byte-exact underlying dataset to extend.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr"/>
-    </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>## 2. Why no extension is attempted</t>
+          <t># S707 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -17865,41 +17881,49 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>- The original raw data (Christodoulopoulos 1995 / Tsoulfidis-Tsaliki 2011) is not redistributed in any public form; Shaikh did not redistribute it in his Appendix 7.2 either.</t>
+          <t>**Series**: S707 — Figure 7.19 — Greek Manufacturing Profit-Rate Deviations, 1962–1991 (Tsoulfidis &amp; Tsaliki 2011 Fig 4)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>- The closest modern source (OECD STAN 2025 for the world / US tracks; ELSTAT post-2010 for the Greek track) has incompatible industry classifications, country coverage, capital-stock coverage, and (for Greece) a 2010 ESYE→ELSTAT methodology break.</t>
+          <t>**Phase**: 6 (Extension)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>- Any modern panel would be a methodologically separate exhibit, not a faithful extension. Per the Anti-Degradation rule, we do not splice.</t>
+          <t>**Construction classification**: `digitized` (book-period figure digitization — recovered 2026-05-26; supersedes the earlier `data_unavailable` classification)</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>**Extension method**: not applicable — no faithful time-extension exists (see §2)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>## 3. Method</t>
+          <t>**Authored**: 2026-05-18 · **Recovery update**: 2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>**Author**: opus-subagent-ch7-fanout</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>N/A.</t>
+          <t>**Related**: `S707_DPR.md`</t>
         </is>
       </c>
     </row>
@@ -17909,7 +17933,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy disclosure</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -17919,7 +17943,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>**None attempted.** No proxy could meet the Anu No-Proxy bar.</t>
+          <t>## 1. Classification</t>
         </is>
       </c>
     </row>
@@ -17929,112 +17953,412 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>## 5. No-Synthetic disclosure</t>
+          <t>`provenance = digitized`, `status = book_period_validated`. This exhibit was **recovered by offline</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>figure digitization**: the plotted coordinates of Tsoulfidis &amp; Tsaliki (2011) Figure 4 — the</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>**None.** No interpolation, no digitization (digitization deferred to Phase 9 visualization, where it is appropriately constrained).</t>
+          <t>20-industry profit-rate-deviation grid Shaikh reproduces as Fig 7.19 — were read directly off the</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>vector-drawn chart in the paper's full text (MPRA working-paper 51334, 2013 revised version),</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>## 6. Failure-mode table</t>
+          <t>per-panel calibrated to each panel's own axis ticks, and clipped to Shaikh's 1962–1991 window.</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Method, validation and caveats are documented in the DPR (`S707_DPR.md` §0) and the extraction</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>| Failure | Action |</t>
+          <t>report (`Technical/WL1_Tsoulfidis_Tsaliki/EXTRACTION_REPORT.md`). There is a recovered book-period</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>|---|---|</t>
+          <t>dataset; there is no byte-exact underlying table to *extend* (that remains obtainable only from the</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>| Loader invoked | Returns `{"status": "SKIPPED", "reason": "data_unavailable"}` — by design, not a failure |</t>
+          <t>original authors).</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>| Validator invoked | Returns `{"status": "PASS_DATA_UNAVAILABLE"}` |</t>
-        </is>
-      </c>
+      <c r="A148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>## 2. Why no time-extension is attempted</t>
+        </is>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
-        </is>
-      </c>
+      <c r="A150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>- The digitized panel reproduces the published figure faithfully but is not the authors' exact</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CD2 had no per-series CSV that matches this exhibit's content. The CD2-vs-RSCD comparison is not meaningful here.</t>
+          <t xml:space="preserve">  tabulated data, and Tsoulfidis &amp; Tsaliki did not redistribute the raw 1962–1991 series.</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>- The closest modern source (ELSTAT — the Greek statistical service, successor to ESYE — for the</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>## 8. Recovery paths (out-of-scope for Phase 6)</t>
+          <t xml:space="preserve">  post-2010 Greek track) has incompatible industry classifications, capital-stock coverage, and a</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr"/>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2010 ESYE→ELSTAT methodology break.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Documented in the B5 provenance file at `SalvagedInputs/book_data/Reconstructed/`. The two most plausible long-term recovery paths are:</t>
+          <t>- Any modern panel would be a methodologically separate exhibit, not a faithful continuation. Per</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1. Author contact (T&amp;T are alive and contactable; Christodoulopoulos last known at NSSR).</t>
+          <t xml:space="preserve">  the Anti-Degradation rule, we do not splice. *(The world/US OECD-ISDB continuation question belongs</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2. PDF figure digitization via WebPlotDigitizer (Phase 9 visualization task; would be flagged `provenance: digitized`).</t>
+          <t xml:space="preserve">  to the separate S703/S704 Christodoulopoulos exhibit, not to this Greek panel.)*</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>## 3. Method</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>No time-extension. The book-period recovery method (offline PDF vector digitization of the source</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>figure) is described in `S707_DPR.md` §0/§4 and the extraction report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>## 4. No-Proxy disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>**None used.** No proxy series stands in for the Greek panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>## 5. No-Synthetic disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>The values are **digitized from the published chart** (`provenance: digitized`) — a documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>figure-digitization recovery of the authors' own plotted points, not fabricated, interpolated, or</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>frozen values. Precision is figure-digitization grade rather than table-exact; the aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Figure-5 validation anchor (DPR §0) reproduces the paper's published moments to ±0.006, confirming</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>the vector pipeline recovers the authors' actual data points. No values were invented where the</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>chart was unreadable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>## 6. Failure-mode table</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>| Failure | Action |</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>| Loader (`L01_S707`) invoked | Reads the digitized panel workbook and emits long-form deviations (no longer SKIPPED) |</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>| Validator (`V03_S707`) invoked | Round-trips against the panel's deviation columns: `PASS`, n=600, MAE 0.0 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>## 7. CD2 divergence pre-disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>CD2 (the predecessor build) had no per-series CSV matching this exhibit's content. The CD2-vs-RSCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>comparison is not meaningful here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>## 8. Remaining recovery path (table-exact, out of scope for Phase 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>The book-period figure has already been recovered by digitization. The only outstanding path to the</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>authors' **exact** tabulated panel is **author contact** (Tsoulfidis &amp; Tsaliki are alive and</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>contactable). That would upgrade the provenance from `digitized` to a redistributed source table;</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>it is not required for the current book-period reproduction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>- **ROP / IROP** — (average) rate of profit / incremental rate of profit (the return on newly added capital).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>- **Digitized (`provenance: digitized`)** — values recovered by reading coordinates off a published chart, faithful to the figure rather than to an exact underlying table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>- **ESYE / ELSTAT** — the Greek national statistical service and its post-2010 successor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>- **ISDB** — OECD International Sectoral Database (relevant to the separate S703/S704 exhibit, not this Greek panel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>- **MPRA** — the Munich Personal RePEc Archive (hosts the full-text source paper, working paper 51334).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>- **L01 / V03** — the load and validate scripts that build and check the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>- **Phase 5 / Phase 6** — Anu pipeline stages: ingestion / extension.</t>
         </is>
       </c>
     </row>
@@ -18550,7 +18874,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-26T18:55:31.153678+00:00</t>
+          <t>2026-07-02T06:25:18.863330+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S707_extenbook.xlsx
+++ b/extenbooks/S707_extenbook.xlsx
@@ -18874,7 +18874,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:25:18.863330+00:00</t>
+          <t>2026-07-11T03:44:26.061599+00:00</t>
         </is>
       </c>
     </row>
@@ -18889,11 +18889,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18916,6 +18916,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TSOULFIDIS_TSALIKI_2011_FIG4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Recovered (2026-05-26) by offline vector extraction of Tsoulfidis &amp; Tsaliki (2011) Fig 4 = Shaikh Fig 7.19 (MPRA 51334), clipped to 1962\u20131991; 20 Greek manufacturing industries. provenance: digitized (faithful to the published figure, not the authors' exact table). Figure 7.19, title, period, and source verified against KB ch07; quotes verbatim-confirmed. Figure-overlay MATCH (point-precision verified on top row) per FIGURE_REPRO_ch07.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S707_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S707_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Phase 3 finding: CD2 S038 link was stale; S707 belongs to Ch7 Fig 7.19; CD2 ancestor disputed. RSCD 2026-05-26: recovered via offline PDF vector extraction of the live MPRA 51334 copy (Fig 4 = vector-drawn 20-industry ROP-deviation panel), clipped to Shaikh's 1962-1991 window; flipped off data_unavailable (provenance: digitized — see subseries source + DPR).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rate deviation (decimal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
